--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104709329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490905</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490906</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490909</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490910</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490911</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109810003</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109810250</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,6 +1788,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/708360</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/708361</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/708364</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2056,6 +2121,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1175461</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109810571</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,6 +2345,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976546</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2376,6 +2456,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976547</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2482,6 +2567,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976548</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109810602</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2698,6 +2793,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104703964</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2804,6 +2904,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1966337</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2917,6 +3022,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104704017</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104706200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,8 +3253,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109810566</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104709329</v>
+        <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92509</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,38 +802,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingstjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513516</v>
+        <v>513438</v>
       </c>
       <c r="R3" t="n">
-        <v>6953008</v>
+        <v>6952671</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,71 +873,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104709329</t>
+          <t>https://artportalen.se/Sighting/135939346</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>490905</v>
+        <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92083</v>
+        <v>92316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>72</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Urskogsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fomitopsis primaeva</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingstjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513404</v>
+        <v>513448</v>
       </c>
       <c r="R4" t="n">
-        <v>6952655</v>
+        <v>6952660</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +965,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Liten fruktkropp på undersidan kolad, fallen kelostubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,42 +984,38 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/490905</t>
+          <t>https://artportalen.se/Sighting/135941720</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>490906</v>
+        <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92083</v>
+        <v>92445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1023,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingtjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513411</v>
+        <v>513419</v>
       </c>
       <c r="R5" t="n">
-        <v>6952638</v>
+        <v>6952641</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,42 +1094,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/490906</t>
+          <t>https://artportalen.se/Sighting/135939082</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>490909</v>
+        <v>104709329</v>
       </c>
       <c r="B6" t="n">
-        <v>92083</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,34 +1129,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513455</v>
+        <v>513516</v>
       </c>
       <c r="R6" t="n">
-        <v>6952877</v>
+        <v>6953008</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1184,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,37 +1210,28 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/490909</t>
+          <t>https://artportalen.se/Sighting/104709329</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>490910</v>
+        <v>490905</v>
       </c>
       <c r="B7" t="n">
         <v>92083</v>
@@ -1272,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513470</v>
+        <v>513404</v>
       </c>
       <c r="R7" t="n">
-        <v>6952898</v>
+        <v>6952655</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,12 +1321,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1342,13 +1336,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/490910</t>
+          <t>https://artportalen.se/Sighting/490905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>490911</v>
+        <v>490906</v>
       </c>
       <c r="B8" t="n">
         <v>92083</v>
@@ -1383,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513538</v>
+        <v>513411</v>
       </c>
       <c r="R8" t="n">
-        <v>6953010</v>
+        <v>6952638</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1438,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1453,13 +1447,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/490911</t>
+          <t>https://artportalen.se/Sighting/490906</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109810003</v>
+        <v>490909</v>
       </c>
       <c r="B9" t="n">
         <v>92083</v>
@@ -1488,17 +1482,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Hemmingstjärnflon, Jmt</t>
+          <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513433</v>
+        <v>513455</v>
       </c>
       <c r="R9" t="n">
-        <v>6952694</v>
+        <v>6952877</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1525,22 +1518,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,28 +1534,37 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Elin Agerberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elin Agerberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109810003</t>
+          <t>https://artportalen.se/Sighting/490909</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109810250</v>
+        <v>490910</v>
       </c>
       <c r="B10" t="n">
         <v>92083</v>
@@ -1601,17 +1593,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Hemmingstjärnflon, Jmt</t>
+          <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513505</v>
+        <v>513470</v>
       </c>
       <c r="R10" t="n">
-        <v>6952635</v>
+        <v>6952898</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,22 +1629,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,53 +1645,62 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Elin Agerberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Elin Agerberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109810250</t>
+          <t>https://artportalen.se/Sighting/490910</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>708360</v>
+        <v>490911</v>
       </c>
       <c r="B11" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1720,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513414</v>
+        <v>513538</v>
       </c>
       <c r="R11" t="n">
-        <v>6952645</v>
+        <v>6953010</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1775,12 +1765,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Elin Agerberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Elin Agerberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1790,51 +1780,52 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/708360</t>
+          <t>https://artportalen.se/Sighting/490911</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>708361</v>
+        <v>109810003</v>
       </c>
       <c r="B12" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingstjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513400</v>
+        <v>513433</v>
       </c>
       <c r="R12" t="n">
-        <v>6952640</v>
+        <v>6952694</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1861,12 +1852,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,75 +1878,67 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/708361</t>
+          <t>https://artportalen.se/Sighting/109810003</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>708364</v>
+        <v>109810250</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingstjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513350</v>
+        <v>513505</v>
       </c>
       <c r="R13" t="n">
-        <v>6952776</v>
+        <v>6952635</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1972,12 +1965,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,78 +1991,72 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Agerberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/708364</t>
+          <t>https://artportalen.se/Sighting/109810250</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1175461</v>
+        <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>93191</v>
+        <v>92229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingtjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513393</v>
+        <v>513419</v>
       </c>
       <c r="R14" t="n">
-        <v>6952783</v>
+        <v>6952641</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,12 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,81 +2094,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1175461</t>
+          <t>https://artportalen.se/Sighting/135939073</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109810571</v>
+        <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>91872</v>
+        <v>92229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Hemmingstjärnflon, Jmt</t>
+          <t>Lill-Hemmingtjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513567</v>
+        <v>513466</v>
       </c>
       <c r="R15" t="n">
-        <v>6952652</v>
+        <v>6952630</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2195,22 +2186,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,71 +2200,75 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109810571</t>
+          <t>https://artportalen.se/Sighting/135939124</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1976546</v>
+        <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>92229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingtjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513379</v>
+        <v>513512</v>
       </c>
       <c r="R16" t="n">
-        <v>6952721</v>
+        <v>6952620</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,12 +2292,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,80 +2306,75 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1976546</t>
+          <t>https://artportalen.se/Sighting/135939188</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1976547</v>
+        <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>92229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingtjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513432</v>
+        <v>513465</v>
       </c>
       <c r="R17" t="n">
-        <v>6952640</v>
+        <v>6952679</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,12 +2398,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,80 +2412,75 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1976547</t>
+          <t>https://artportalen.se/Sighting/135939252</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1976548</v>
+        <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>92229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näveråstjärn, Jmt</t>
+          <t>Lill-Hemmingtjärnsflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513483</v>
+        <v>513438</v>
       </c>
       <c r="R18" t="n">
-        <v>6952593</v>
+        <v>6952691</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,12 +2504,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,42 +2518,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sara Toivanen Jonsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1976548</t>
+          <t>https://artportalen.se/Sighting/135939323</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109810602</v>
+        <v>708360</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,35 +2553,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Hemmingstjärnflon, Jmt</t>
+          <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513575</v>
+        <v>513414</v>
       </c>
       <c r="R19" t="n">
-        <v>6952671</v>
+        <v>6952645</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2641,22 +2607,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,67 +2623,75 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109810602</t>
+          <t>https://artportalen.se/Sighting/708360</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104703964</v>
+        <v>708361</v>
       </c>
       <c r="B20" t="n">
-        <v>80336</v>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Näveråstjärn, märlingsberget, Jmt</t>
+          <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513517</v>
+        <v>513400</v>
       </c>
       <c r="R20" t="n">
-        <v>6952784</v>
+        <v>6952640</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2754,22 +2718,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,31 +2734,40 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104703964</t>
+          <t>https://artportalen.se/Sighting/708361</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1966337</v>
+        <v>708364</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>91962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2836,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513464</v>
+        <v>513350</v>
       </c>
       <c r="R21" t="n">
-        <v>6952953</v>
+        <v>6952776</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2906,16 +2869,16 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1966337</t>
+          <t>https://artportalen.se/Sighting/708364</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104704017</v>
+        <v>1175461</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>93191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,40 +2886,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näveråstjärn , Jmt</t>
+          <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513718</v>
+        <v>513393</v>
       </c>
       <c r="R22" t="n">
-        <v>6952866</v>
+        <v>6952783</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2983,22 +2940,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:53</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:53</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,72 +2956,76 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104704017</t>
+          <t>https://artportalen.se/Sighting/1175461</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104706200</v>
+        <v>109810571</v>
       </c>
       <c r="B23" t="n">
-        <v>5495</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101410</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näveråstjärn , Jmt</t>
+          <t>Lill-Hemmingstjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513659</v>
+        <v>513567</v>
       </c>
       <c r="R23" t="n">
-        <v>6953168</v>
+        <v>6952652</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,22 +3052,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,16 +3093,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104706200</t>
+          <t>https://artportalen.se/Sighting/109810571</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109810566</v>
+        <v>1976546</v>
       </c>
       <c r="B24" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,35 +3110,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Hemmingstjärnflon, Jmt</t>
+          <t>Näveråstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513567</v>
+        <v>513379</v>
       </c>
       <c r="R24" t="n">
-        <v>6952652</v>
+        <v>6952721</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,22 +3164,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,20 +3180,937 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976546</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1976547</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Näveråstjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>513432</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6952640</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976547</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1976548</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Näveråstjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>513483</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6952593</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976548</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>109810602</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Hemmingstjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>513575</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6952671</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109810602</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104703964</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Näveråstjärn, märlingsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>513517</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6952784</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104703964</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1966337</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Näveråstjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>513464</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6952953</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Agerberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Agerberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1966337</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>104704017</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Näveråstjärn , Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>513718</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6952866</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104704017</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104706200</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Näveråstjärn , Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>513659</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6953168</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104706200</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>109810566</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lill-Hemmingstjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>513567</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6952652</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109810566</t>
         </is>
@@ -3284,6 +4141,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92316</v>
+        <v>92330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92445</v>
+        <v>92459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92330</v>
+        <v>92331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92332</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92333</v>
+        <v>92339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92462</v>
+        <v>92468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 1938-2022 artfynd.xlsx
+++ b/artfynd/S 1938-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135939346</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135941720</v>
       </c>
       <c r="B4" t="n">
-        <v>92339</v>
+        <v>92340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>135939082</v>
       </c>
       <c r="B5" t="n">
-        <v>92468</v>
+        <v>92469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135939073</v>
       </c>
       <c r="B14" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135939124</v>
       </c>
       <c r="B15" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135939188</v>
       </c>
       <c r="B16" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135939252</v>
       </c>
       <c r="B17" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>135939323</v>
       </c>
       <c r="B18" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
